--- a/docs/ValueSet-ahip-care-consideration.xlsx
+++ b/docs/ValueSet-ahip-care-consideration.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="42">
   <si>
     <t>Property</t>
   </si>
@@ -50,7 +50,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T00:00:00-04:00</t>
+    <t>2026-08-25T00:00:00-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -86,7 +86,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>AHIP Care Consideration Codes</t>
+    <t>Used as the answer options for the care considerations question in the Spirituality and Other Considerations Section, letting a patient flag considerations they want their care team to know before providing care.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -104,51 +104,21 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
+    <t>Codes</t>
+  </si>
+  <si>
+    <t>All codes</t>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/care-consideration</t>
+  </si>
+  <si>
     <t>Concept</t>
   </si>
   <si>
-    <t>HEBE</t>
-  </si>
-  <si>
-    <t>Health beliefs</t>
-  </si>
-  <si>
-    <t>CUPR</t>
-  </si>
-  <si>
-    <t>Cultural preferences</t>
-  </si>
-  <si>
-    <t>REBE</t>
-  </si>
-  <si>
-    <t>Religious beliefs (e.g., no blood transfusions, need or want particular people in the room with you or before procedures or for end of life rituals, etc.)</t>
-  </si>
-  <si>
-    <t>SPBE</t>
-  </si>
-  <si>
-    <t>Spiritual beliefs</t>
-  </si>
-  <si>
-    <t>DIET</t>
-  </si>
-  <si>
-    <t>Specific diet followed (e.g., Halal, Kosher, Pescatarian, Vegetarian, Vegan)</t>
-  </si>
-  <si>
-    <t>CARE</t>
-  </si>
-  <si>
-    <t>Caregiving status</t>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>http://ahip.org/demographics/ImplementationGuide/ahip.demo/CodeSystem/ahip-demo-additional-care-consideration-codes</t>
-  </si>
-  <si>
     <t>ASKU</t>
   </si>
   <si>
@@ -170,7 +140,7 @@
     <t>Please specify if not listed above</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/ImplementationGuide/ahip.demo/CodeSystem/AHIPDemoAdditionalNullFlavor</t>
+    <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
   </si>
 </sst>
 </file>
@@ -436,7 +406,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -447,72 +417,26 @@
       <c r="A1" t="s" s="1">
         <v>29</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>22</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>31</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -531,7 +455,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>22</v>
@@ -539,10 +463,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -555,10 +479,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -577,7 +501,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>22</v>
@@ -585,18 +509,18 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -609,10 +533,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-ahip-care-consideration.xlsx
+++ b/docs/ValueSet-ahip-care-consideration.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
   <si>
     <t>Property</t>
   </si>
@@ -132,12 +132,6 @@
   </si>
   <si>
     <t>I choose not to respond at this time</t>
-  </si>
-  <si>
-    <t>PSIN</t>
-  </si>
-  <si>
-    <t>Please specify if not listed above</t>
   </si>
   <si>
     <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
@@ -492,7 +486,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -517,26 +511,18 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-ahip-care-consideration.xlsx
+++ b/docs/ValueSet-ahip-care-consideration.xlsx
@@ -9,13 +9,12 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
-    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
   <si>
     <t>Property</t>
   </si>
@@ -95,7 +94,8 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Used by permission of HL7 International, all rights reserved Creative Commons License</t>
+    <t>This material derives from the HL7 Terminology (THO). THO is copyright ©1989+ Health Level Seven International and is made available under the CC0 designation. For more licensing information see: https://terminology.hl7.org/license.html
+This value set includes content developed through the DEMo Initiative and is subject to joint copyright of America's Health Insurance Plans (AHIP) and Health Level Seven International (HL7).</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -119,22 +119,13 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>ASKU</t>
-  </si>
-  <si>
-    <t>Asked but unknown</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/v3-NullFlavor</t>
-  </si>
-  <si>
     <t>CNTR</t>
   </si>
   <si>
     <t>I choose not to respond at this time</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
+    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-additional-nullFlavor</t>
   </si>
 </sst>
 </file>
@@ -482,50 +473,4 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>33</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>